--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_915_Sweden_West_Coast.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_915_Sweden_West_Coast.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Ree0636fc1e6043b9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Re546bed3ae4940e5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R0b4bed6de5194006"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R7042bf46a0104a5f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R74e9e56043d144aa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R3cb5cb8ffb784b21"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R2b97d678bdfb4d43"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R9954b31ed081477f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Ra339bb54594041b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R3148bc6de3d1493e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rab101f05ab354c8c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R950ae14488314c5a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ915CommercialTable" displayName="EEZ915CommercialTable" ref="A1:O12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O12"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ915CommercialTable" displayName="EEZ915CommercialTable" ref="A1:E12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E12"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ915FunctionalTable" displayName="EEZ915FunctionalTable" ref="A1:O25" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O25"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ915FunctionalTable" displayName="EEZ915FunctionalTable" ref="A1:E25" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E25"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ915ValidationTable" displayName="EEZ915ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ915ValidationTable" displayName="EEZ915ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -8533,7 +8487,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6842f9b334fc47b4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4e12753e1f11482b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8543,20 +8497,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -8564,660 +8508,231 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>0.2464960979</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.11</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>128.82495516931337</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>0.2464960979</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$118,A2,'Species'!$U$2:$U$118))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>31.754848761378177</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.11</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>31.754848761378177</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>3614.2285225071</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.067651698111524</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>1168.5618346720862</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>3614.2285225071</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>1300.0982060397764</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$118,A3,'Species'!$U$2:$U$118))</x:f>
-        <x:v>4698852.018329272</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.067651698111524</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>1168.5618346720862</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>4223449.51318508</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>475402.5051441919</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.1125626111215594</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.11256261112155949</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>2020.2925280815002</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>2.9298031604604153</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>85.0752355986921</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>2020.2925280815002</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>87.26075235234381</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$118,A4,'Species'!$U$2:$U$118))</x:f>
-        <x:v>176292.2459722104</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>2.9298031604604153</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>85.0752355986921</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>171876.86280481092</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>4415.383167399472</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0256892236415422</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.025689223641542303</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>2765.0322664091</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.3031046139445706</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>200.95768262196867</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>2765.0322664091</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>254.5785685487874</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$118,A5,'Species'!$U$2:$U$118))</x:f>
-        <x:v>703917.956373638</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.3031046139445706</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>200.95768262196867</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>555654.4766325427</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>148263.47974109533</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.2668267529123909</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.2668267529123909</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>4934.2341779027</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.272136288263288</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>187.1269281208731</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>4934.2341779027</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>199.78304333802748</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$118,A6,'Species'!$U$2:$U$118))</x:f>
-        <x:v>985776.3206039115</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.272136288263288</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>187.1269281208731</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>923328.0843399538</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>62448.23626395769</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0676338533649166</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.0676338533649165</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>385.0249028247</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.010466539547393</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>10.243928523700522</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>385.0249028247</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>11.926377240604022</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$118,A7,'Species'!$U$2:$U$118))</x:f>
-        <x:v>4591.952238114278</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.010466539547393</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>10.243928523700522</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>3944.1675843809658</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>647.7846537333121</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.1642386232011441</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.16423862320114407</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>372.3682844967</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.6963117121685474</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>496.94887544841356</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>372.3682844967</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1054.8021647988273</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$118,A8,'Species'!$U$2:$U$118))</x:f>
-        <x:v>392774.8725895448</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.6963117121685474</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>496.94887544841356</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>185048.00023329002</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>207726.87235625478</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>2.122556699312468</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>1.1225566993124676</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>338.8228388027999</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.788185755657395</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>614.024578499266</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>338.8228388027999</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>729.0874125403894</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$118,A9,'Species'!$U$2:$U$118))</x:f>
-        <x:v>247031.46685232283</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.788185755657395</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>614.024578499266</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>208045.55078181394</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>38985.91607050889</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.1873912512139952</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.18739125121399516</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Salmon, smelts, etc</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>0.9640786274</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.865394327153611</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>733.4902193345741</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>0.9640786274</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>1529.9086172206416</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$118,A10,'Species'!$U$2:$U$118))</x:f>
-        <x:v>1474.9521997375082</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.865394327153611</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>733.4902193345741</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>707.1422438674012</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>767.8099558701069</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>2.08579279844874</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>1.0857927984487399</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>32.709811531499994</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.896460212434686</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>787.8802470831313</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>32.709811531499994</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>789.8716837068662</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$118,A11,'Species'!$U$2:$U$118))</x:f>
-        <x:v>25836.553908120168</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.896460212434686</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>787.8802470831313</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>25771.414391480874</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>65.13951663929402</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.002527587956555</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.0025275879565549515</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>18.118080681200006</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.9675470294413606</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>927.9979769290188</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>18.118080681200006</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>1080.863455314543</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$H$2:$H$118,A12,'Species'!$U$2:$U$118))</x:f>
-        <x:v>19583.171288749505</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.9675470294413606</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>927.9979769290188</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>16813.542217990343</x:v>
       </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>2769.6290707591616</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.1647260901272596</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.16472609012725958</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G12">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O12">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R576e3e4b137b4df2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbc369a9fd7bd49fc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9227,20 +8742,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -9248,1362 +8753,478 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>12.432607679799997</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.806532393312625</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>640.5195550900153</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>12.432607679799997</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>654.4713209265957</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$118,A2,'Species'!$U$2:$U$118))</x:f>
-        <x:v>8136.785170760842</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.806532393312625</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>640.5195550900153</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>7963.328339674201</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>173.4568310866416</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0217819514263227</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.021781951426322596</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>112.9876434982</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.449999102532482</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>2818.377107095311</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>112.9876434982</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2818.3777289881496</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$118,A3,'Species'!$U$2:$U$118))</x:f>
-        <x:v>318441.8580861796</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.449999102532482</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>2818.377107095311</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>318441.78781997325</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0.07026620634132996</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0000002206563618</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>2.2065636178708432e-7</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large bathypelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>0.1339149218</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.543381454388453</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>349.44711102116025</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>0.1339149218</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>356.65416589720166</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$118,A4,'Species'!$U$2:$U$118))</x:f>
-        <x:v>47.76131473576799</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.543381454388453</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>349.44711102116025</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>46.79618254563459</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>0.9651321901333958</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0206241649987629</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.02062416499876289</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>2674.4884107263997</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.093188299672349</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>1239.333815478548</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>2674.4884107263997</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>1242.2408692162805</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$118,A5,'Species'!$U$2:$U$118))</x:f>
-        <x:v>3322358.8080496313</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.093188299672349</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>1239.333815478548</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>3314583.926518707</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>7774.8815309242345</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0023456583701864</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.0023456583701864982</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>503.5842469824</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.2799016977640045</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>1905.0294671421525</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>503.5842469824</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>2066.1463121777933</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$118,A6,'Species'!$U$2:$U$118))</x:f>
-        <x:v>1040478.7347735168</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.2799016977640045</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>1905.0294671421525</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>959342.8296900635</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>81135.90508345328</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0845744634477186</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.08457446344771868</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large flatfishes (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>2087.9910472872</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.286932590298801</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>193.61214224903915</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>2087.9910472872</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>231.53071847007132</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$118,A7,'Species'!$U$2:$U$118))</x:f>
-        <x:v>483434.0673374821</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.286932590298801</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>193.61214224903915</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>404260.41966208967</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>79173.64767539245</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.1958481311169953</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.19584813111699523</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>0.5150983987000001</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.36</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>229.08676527677724</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>0.5150983987000001</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>229.08676527677724</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$118,A8,'Species'!$U$2:$U$118))</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>118.00222595743074</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.36</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>229.08676527677724</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
-        <x:v>118.00222595743074</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>1.6212852735</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.5729381705483054</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>374.05733084643083</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>1.6212852735</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>381.7299330411452</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$118,A9,'Species'!$U$2:$U$118))</x:f>
-        <x:v>618.8931188937498</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.5729381705483054</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>374.05733084643083</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>606.4536419460356</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>12.439476947714184</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0205118348498945</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.02051183484989458</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>0.0088200624</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.79</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>616.5950018614822</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>0.0088200624</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>616.5950018614822</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$118,A10,'Species'!$U$2:$U$118))</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>5.438406391946389</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.79</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>616.5950018614822</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
-        <x:v>5.438406391946389</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>1.0129604239</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.365353077426385</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>2319.2794365954296</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>1.0129604239</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>2324.3849667936893</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$118,A11,'Species'!$U$2:$U$118))</x:f>
-        <x:v>2354.5099812701233</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.365353077426385</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>2319.2794365954296</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>2349.3382812362597</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>5.171700033863544</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0022013432783048</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.0022013432783047795</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>1533.6626048401</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>2.8855937454346754</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>76.84113046151663</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>1533.6626048401</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>77.71456167018455</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$118,A12,'Species'!$U$2:$U$118))</x:f>
-        <x:v>119187.91708510181</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>2.8855937454346754</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>76.84113046151663</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>117848.36830246754</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>1339.5487826342724</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0113667147193435</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.011366714719343505</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>1.2140630869</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>4.430705916181991</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>2695.9132684193937</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>1.2140630869</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>2809.237810745585</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$118,A13,'Species'!$U$2:$U$118))</x:f>
-        <x:v>3410.591928349983</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>4.430705916181991</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>2695.9132684193937</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>3273.0087846719175</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>137.58314367806543</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.0420356780960662</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.042035678096066155</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>412.4237670496</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.598300843229981</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>396.55263794101757</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>412.4237670496</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>682.7098166239338</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$118,A14,'Species'!$U$2:$U$118))</x:f>
-        <x:v>281565.75437378435</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.598300843229981</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>396.55263794101757</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>163547.7327730906</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>118018.02160069376</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.7216120920761055</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.7216120920761055</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>387.76066787319996</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.649411518711757</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>446.0787331614984</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>387.76066787319996</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>681.2084509817237</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$118,A15,'Species'!$U$2:$U$118))</x:f>
-        <x:v>264145.8439135412</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.649411518711757</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>446.0787331614984</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>172971.78749473358</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>91174.0564188076</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.527103626200218</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.527103626200218</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>3741.0288769915005</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.4004719673893176</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>251.46176955431008</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>3741.0288769915005</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>257.6625054422739</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$118,A16,'Species'!$U$2:$U$118))</x:f>
-        <x:v>963922.8733775264</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.4004719673893176</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>251.46176955431008</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>940725.7413620561</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>23197.1320154703</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.0246587618426213</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.024658761842621297</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>4.3832966493</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.1997358473207176</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>158.39294996059724</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>4.3832966493</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>158.48724775964794</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$118,A17,'Species'!$U$2:$U$118))</x:f>
-        <x:v>694.6966220616438</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.1997358473207176</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>158.39294996059724</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>694.2832868350284</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>0.41333522661534516</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.0005953408852741</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.0005953408852740531</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>385.0249028247</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>2.010466539547393</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>10.243928523700522</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>385.0249028247</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>11.926377240604022</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$118,A18,'Species'!$U$2:$U$118))</x:f>
-        <x:v>4591.952238114278</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>2.010466539547393</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>10.243928523700522</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>3944.1675843809658</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>647.7846537333121</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.1642386232011441</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.16423862320114407</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>486.62992324140004</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.0691335291216957</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>117.25558266843797</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>486.62992324140004</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>117.3465217813602</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$118,A19,'Species'!$U$2:$U$118))</x:f>
-        <x:v>57104.32888710859</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.0691335291216957</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>117.25558266843797</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>57060.0751935676</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>44.253693540988024</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.0007755631830288</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.0007755631830288362</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>0.0839616992</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.31</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>204.17379446695296</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>0.0839616992</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>204.17379446695296</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$118,A20,'Species'!$U$2:$U$118))</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>17.14277871555693</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.31</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>204.17379446695296</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
-        <x:v>17.14277871555693</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>1438.6950306223002</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>3.0100179290096514</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>102.33352378293556</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>1438.6950306223002</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>102.33406274561969</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$118,A21,'Species'!$U$2:$U$118))</x:f>
-        <x:v>147227.50753551372</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>3.0100179290096514</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>102.33352378293556</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>147226.73213257836</x:v>
-      </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>0.7754029353673104</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1.0000052667265253</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0.000005266726525377582</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="18" customHeight="1">
       <x:c r="A22" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B22" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C22" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D22" s="31" t="n">
+      <x:c r="B22" s="31" t="n">
         <x:v>3.8338037244000005</x:v>
       </x:c>
+      <x:c r="C22" s="32" t="n">
+        <x:v>3.4865149978286665</x:v>
+      </x:c>
+      <x:c r="D22" s="32" t="n">
+        <x:f>IF(C22="","",(1/'Metadata'!$B$5)^(C22-1))</x:f>
+        <x:v>306.55965442243775</x:v>
+      </x:c>
       <x:c r="E22" s="31" t="n">
-        <x:v>3.8338037244000005</x:v>
-      </x:c>
-      <x:c r="F22" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H22" s="32" t="n">
-        <x:f>IF(E22=0,"",I22/E22)</x:f>
-        <x:v>314.6068139394348</x:v>
-      </x:c>
-      <x:c r="I22" s="31" t="n">
-        <x:f>IF(C22=0,"",SUMIF('Species'!$G$2:$G$118,A22,'Species'!$U$2:$U$118))</x:f>
-        <x:v>1206.140775002623</x:v>
-      </x:c>
-      <x:c r="J22" s="32" t="n">
-        <x:v>3.4865149978286665</x:v>
-      </x:c>
-      <x:c r="K22" s="32" t="n">
-        <x:f>IF(J22="","",(1/'Metadata'!$B$5)^(J22-1))</x:f>
-        <x:v>306.55965442243775</x:v>
-      </x:c>
-      <x:c r="L22" s="31" t="n">
-        <x:f>IF(E22=0,"",E22*K22)</x:f>
+        <x:f>IF(B22=0,"",B22*D22)</x:f>
         <x:v>1175.289544875519</x:v>
-      </x:c>
-      <x:c r="M22" s="31" t="n">
-        <x:f>IF(E22=0,"",I22-L22)</x:f>
-        <x:v>30.851230127104145</x:v>
-      </x:c>
-      <x:c r="N22" s="32" t="n">
-        <x:f>IF(L22=0,"",I22/L22)</x:f>
-        <x:v>1.0262498975351404</x:v>
-      </x:c>
-      <x:c r="O22" s="34" t="n">
-        <x:f>IF(L22=0,"",M22/L22)</x:f>
-        <x:v>0.02624989753514038</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="18" customHeight="1">
       <x:c r="A23" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B23" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C23" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D23" s="31" t="n">
+      <x:c r="B23" s="31" t="n">
         <x:v>677.0412191219</x:v>
       </x:c>
+      <x:c r="C23" s="32" t="n">
+        <x:v>3.3529790375914437</x:v>
+      </x:c>
+      <x:c r="D23" s="32" t="n">
+        <x:f>IF(C23="","",(1/'Metadata'!$B$5)^(C23-1))</x:f>
+        <x:v>225.41304077699016</x:v>
+      </x:c>
       <x:c r="E23" s="31" t="n">
-        <x:v>677.0412191219</x:v>
-      </x:c>
-      <x:c r="F23" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G23" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H23" s="32" t="n">
-        <x:f>IF(E23=0,"",I23/E23)</x:f>
-        <x:v>325.6579995559445</x:v>
-      </x:c>
-      <x:c r="I23" s="31" t="n">
-        <x:f>IF(C23=0,"",SUMIF('Species'!$G$2:$G$118,A23,'Species'!$U$2:$U$118))</x:f>
-        <x:v>220483.88903615583</x:v>
-      </x:c>
-      <x:c r="J23" s="32" t="n">
-        <x:v>3.3529790375914437</x:v>
-      </x:c>
-      <x:c r="K23" s="32" t="n">
-        <x:f>IF(J23="","",(1/'Metadata'!$B$5)^(J23-1))</x:f>
-        <x:v>225.41304077699016</x:v>
-      </x:c>
-      <x:c r="L23" s="31" t="n">
-        <x:f>IF(E23=0,"",E23*K23)</x:f>
+        <x:f>IF(B23=0,"",B23*D23)</x:f>
         <x:v>152613.91993362797</x:v>
-      </x:c>
-      <x:c r="M23" s="31" t="n">
-        <x:f>IF(E23=0,"",I23-L23)</x:f>
-        <x:v>67869.96910252786</x:v>
-      </x:c>
-      <x:c r="N23" s="32" t="n">
-        <x:f>IF(L23=0,"",I23/L23)</x:f>
-        <x:v>1.4447167671995098</x:v>
-      </x:c>
-      <x:c r="O23" s="34" t="n">
-        <x:f>IF(L23=0,"",M23/L23)</x:f>
-        <x:v>0.4447167671995098</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="18" customHeight="1">
       <x:c r="A24" s="24" t="str">
         <x:v>Small to medium rays (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B24" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C24" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D24" s="31" t="n">
+      <x:c r="B24" s="31" t="n">
         <x:v>15.4396132984</x:v>
       </x:c>
+      <x:c r="C24" s="32" t="n">
+        <x:v>3.983307561932286</x:v>
+      </x:c>
+      <x:c r="D24" s="32" t="n">
+        <x:f>IF(C24="","",(1/'Metadata'!$B$5)^(C24-1))</x:f>
+        <x:v>962.2935213941587</x:v>
+      </x:c>
       <x:c r="E24" s="31" t="n">
-        <x:v>15.4396132984</x:v>
-      </x:c>
-      <x:c r="F24" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G24" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H24" s="32" t="n">
-        <x:f>IF(E24=0,"",I24/E24)</x:f>
-        <x:v>1073.8967932895202</x:v>
-      </x:c>
-      <x:c r="I24" s="31" t="n">
-        <x:f>IF(C24=0,"",SUMIF('Species'!$G$2:$G$118,A24,'Species'!$U$2:$U$118))</x:f>
-        <x:v>16580.551210781992</x:v>
-      </x:c>
-      <x:c r="J24" s="32" t="n">
-        <x:v>3.983307561932286</x:v>
-      </x:c>
-      <x:c r="K24" s="32" t="n">
-        <x:f>IF(J24="","",(1/'Metadata'!$B$5)^(J24-1))</x:f>
-        <x:v>962.2935213941587</x:v>
-      </x:c>
-      <x:c r="L24" s="31" t="n">
-        <x:f>IF(E24=0,"",E24*K24)</x:f>
+        <x:f>IF(B24=0,"",B24*D24)</x:f>
         <x:v>14857.439849881417</x:v>
-      </x:c>
-      <x:c r="M24" s="31" t="n">
-        <x:f>IF(E24=0,"",I24-L24)</x:f>
-        <x:v>1723.1113609005752</x:v>
-      </x:c>
-      <x:c r="N24" s="32" t="n">
-        <x:f>IF(L24=0,"",I24/L24)</x:f>
-        <x:v>1.1159763309366066</x:v>
-      </x:c>
-      <x:c r="O24" s="34" t="n">
-        <x:f>IF(L24=0,"",M24/L24)</x:f>
-        <x:v>0.11597633093660668</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="18" customHeight="1">
       <x:c r="A25" s="24" t="str">
         <x:v>Small to medium sharks (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B25" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C25" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D25" s="31" t="n">
+      <x:c r="B25" s="31" t="n">
         <x:v>0.0442216854</x:v>
       </x:c>
+      <x:c r="C25" s="32" t="n">
+        <x:v>3.82</x:v>
+      </x:c>
+      <x:c r="D25" s="32" t="n">
+        <x:f>IF(C25="","",(1/'Metadata'!$B$5)^(C25-1))</x:f>
+        <x:v>660.6934480075957</x:v>
+      </x:c>
       <x:c r="E25" s="31" t="n">
-        <x:v>0.0442216854</x:v>
-      </x:c>
-      <x:c r="F25" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G25" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H25" s="32" t="n">
-        <x:f>IF(E25=0,"",I25/E25)</x:f>
-        <x:v>660.6934480075957</x:v>
-      </x:c>
-      <x:c r="I25" s="31" t="n">
-        <x:f>IF(C25=0,"",SUMIF('Species'!$G$2:$G$118,A25,'Species'!$U$2:$U$118))</x:f>
+        <x:f>IF(B25=0,"",B25*D25)</x:f>
         <x:v>29.216977803633156</x:v>
       </x:c>
-      <x:c r="J25" s="32" t="n">
-        <x:v>3.82</x:v>
-      </x:c>
-      <x:c r="K25" s="32" t="n">
-        <x:f>IF(J25="","",(1/'Metadata'!$B$5)^(J25-1))</x:f>
-        <x:v>660.6934480075957</x:v>
-      </x:c>
-      <x:c r="L25" s="31" t="n">
-        <x:f>IF(E25=0,"",E25*K25)</x:f>
-        <x:v>29.216977803633156</x:v>
-      </x:c>
-      <x:c r="M25" s="31" t="n">
-        <x:f>IF(E25=0,"",I25-L25)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N25" s="32" t="n">
-        <x:f>IF(L25=0,"",I25/L25)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O25" s="34" t="n">
-        <x:f>IF(L25=0,"",M25/L25)</x:f>
-        <x:v>0</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G25">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O25">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd224a3018c594c77"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1cf8a58536bb464b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10778,7 +9399,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -10877,7 +9498,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>7256163.265204381</x:v>
+        <x:v>6314670.509263973</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -10891,7 +9512,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>7256163.265204381</x:v>
+        <x:v>6783703.22676787</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -10905,7 +9526,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-941492.7559404084</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -10919,7 +9540,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-472460.03843651153</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -10930,9 +9551,9 @@
         <x:v>EEZ_915</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -10944,47 +9565,19 @@
         <x:v>EEZ_915</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_915</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_915</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf77a2602cbb54e66"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4c471e21cc1e4bd5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11031,7 +9624,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
